--- a/public/UserManagement/template-registrasi-mahasiswa.xlsx
+++ b/public/UserManagement/template-registrasi-mahasiswa.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\S-6\PROYEK 3\ril cuy\sipta\public\UserManagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\S-6\PROYEK 3\sinta-app-dev\sipta\public\UserManagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47DA2DB6-5A6A-4E5A-9127-98A733878CF0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7B3A8C2-A6FF-4885-BCBF-0B97EE479630}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B283ADED-F7A5-4761-92DA-B96BF34ED6BB}"/>
   </bookViews>
@@ -45,10 +45,10 @@
     <t>NIM</t>
   </si>
   <si>
-    <t>Kelas</t>
-  </si>
-  <si>
     <t>No Whatsapp (jika kosong isi -)</t>
+  </si>
+  <si>
+    <t>Kelas (A/B/C/D)</t>
   </si>
 </sst>
 </file>
@@ -416,6 +416,7 @@
     <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="30.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -433,10 +434,10 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
       </c>
       <c r="G1" s="1"/>
     </row>
